--- a/data/SKU_grupos_precios.xlsx
+++ b/data/SKU_grupos_precios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://accmotos-my.sharepoint.com/personal/analista_ecommerce_accemotos_com/Documents/Catalogo Skill/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{0B29A6C5-0BF4-46B9-A3A7-B4C4E4CF4400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{848647C5-4F63-4175-9C09-C684DE38AEA0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C285A495-2355-40BF-820D-432B750315B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74CAEB48-B1FB-431F-B1BD-2917AA7C7075}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SKUs_Totales!$A$1:$H$1626</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -8734,7 +8734,7 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>2572</v>
+        <v>2550</v>
       </c>
       <c r="E14" s="9">
         <v>37300</v>
@@ -8760,7 +8760,7 @@
         <v>28</v>
       </c>
       <c r="D15">
-        <v>2628</v>
+        <v>2615</v>
       </c>
       <c r="E15" s="9">
         <v>37300</v>
@@ -9112,7 +9112,7 @@
         <v>56</v>
       </c>
       <c r="D29">
-        <v>1867</v>
+        <v>1767</v>
       </c>
       <c r="E29" s="9">
         <v>10772</v>
@@ -9230,7 +9230,7 @@
         <v>67</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="E34" s="9">
         <v>75000</v>
@@ -10040,7 +10040,7 @@
         <v>121</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="9">
         <v>185500</v>
@@ -10456,7 +10456,7 @@
         <v>146</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E83" s="9">
         <v>185500</v>
@@ -10508,7 +10508,7 @@
         <v>146</v>
       </c>
       <c r="D85">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E85" s="9">
         <v>185500</v>
@@ -10586,7 +10586,7 @@
         <v>153</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" s="9">
         <v>185500</v>
@@ -10638,7 +10638,7 @@
         <v>153</v>
       </c>
       <c r="D90">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E90" s="9">
         <v>185500</v>
@@ -10716,7 +10716,7 @@
         <v>157</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E93" s="9">
         <v>185500</v>
@@ -10794,7 +10794,7 @@
         <v>161</v>
       </c>
       <c r="D96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E96" s="9">
         <v>185500</v>
@@ -10872,7 +10872,7 @@
         <v>165</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="9">
         <v>185500</v>
@@ -10898,7 +10898,7 @@
         <v>169</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="9">
         <v>185500</v>
@@ -10950,7 +10950,7 @@
         <v>169</v>
       </c>
       <c r="D102">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E102" s="9">
         <v>185500</v>
@@ -13310,7 +13310,7 @@
         <v>318</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="E193" s="9">
         <v>81000</v>
@@ -13336,7 +13336,7 @@
         <v>318</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E194" s="9">
         <v>81000</v>
@@ -13362,7 +13362,7 @@
         <v>318</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E195" s="9">
         <v>81000</v>
@@ -13388,7 +13388,7 @@
         <v>318</v>
       </c>
       <c r="D196">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E196" s="9">
         <v>81000</v>
@@ -13414,7 +13414,7 @@
         <v>323</v>
       </c>
       <c r="D197">
-        <v>547</v>
+        <v>783</v>
       </c>
       <c r="E197" s="9">
         <v>81000</v>
@@ -13440,7 +13440,7 @@
         <v>323</v>
       </c>
       <c r="D198">
-        <v>98</v>
+        <v>210</v>
       </c>
       <c r="E198" s="9">
         <v>81000</v>
@@ -13466,7 +13466,7 @@
         <v>323</v>
       </c>
       <c r="D199">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="E199" s="9">
         <v>81000</v>
@@ -13492,7 +13492,7 @@
         <v>323</v>
       </c>
       <c r="D200">
-        <v>226</v>
+        <v>440</v>
       </c>
       <c r="E200" s="9">
         <v>81000</v>
@@ -13518,7 +13518,7 @@
         <v>328</v>
       </c>
       <c r="D201">
-        <v>99</v>
+        <v>454</v>
       </c>
       <c r="E201" s="9">
         <v>81000</v>
@@ -13544,7 +13544,7 @@
         <v>328</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="E202" s="9">
         <v>81000</v>
@@ -13570,7 +13570,7 @@
         <v>328</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="E203" s="9">
         <v>81000</v>
@@ -13596,7 +13596,7 @@
         <v>328</v>
       </c>
       <c r="D204">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="E204" s="9">
         <v>81000</v>
@@ -15020,7 +15020,7 @@
         <v>430</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259" s="9">
         <v>138500</v>
@@ -15150,7 +15150,7 @@
         <v>437</v>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264" s="9">
         <v>138500</v>
@@ -15306,7 +15306,7 @@
         <v>445</v>
       </c>
       <c r="D270">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E270" s="9">
         <v>138500</v>
@@ -15774,7 +15774,7 @@
         <v>472</v>
       </c>
       <c r="D288">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E288" s="9">
         <v>138500</v>
@@ -15826,7 +15826,7 @@
         <v>476</v>
       </c>
       <c r="D290">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E290" s="9">
         <v>138500</v>
@@ -15956,7 +15956,7 @@
         <v>482</v>
       </c>
       <c r="D295">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E295" s="9">
         <v>138500</v>
@@ -16060,7 +16060,7 @@
         <v>489</v>
       </c>
       <c r="D299">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E299" s="9">
         <v>138500</v>
@@ -16164,7 +16164,7 @@
         <v>498</v>
       </c>
       <c r="D303">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E303" s="9">
         <v>138500</v>
@@ -16216,7 +16216,7 @@
         <v>498</v>
       </c>
       <c r="D305">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E305" s="9">
         <v>138500</v>
@@ -16554,7 +16554,7 @@
         <v>519</v>
       </c>
       <c r="D318">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E318" s="9">
         <v>92521</v>
@@ -16606,7 +16606,7 @@
         <v>519</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E320" s="9">
         <v>92521</v>
@@ -16658,7 +16658,7 @@
         <v>519</v>
       </c>
       <c r="D322">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E322" s="9">
         <v>92521</v>
@@ -16710,7 +16710,7 @@
         <v>523</v>
       </c>
       <c r="D324">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E324" s="9">
         <v>92521</v>
@@ -16788,7 +16788,7 @@
         <v>523</v>
       </c>
       <c r="D327">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E327" s="9">
         <v>92521</v>
@@ -17334,7 +17334,7 @@
         <v>553</v>
       </c>
       <c r="D348">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E348" s="9">
         <v>92521</v>
@@ -17438,7 +17438,7 @@
         <v>559</v>
       </c>
       <c r="D352">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E352" s="9">
         <v>92521</v>
@@ -17464,7 +17464,7 @@
         <v>559</v>
       </c>
       <c r="D353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E353" s="9">
         <v>92521</v>
@@ -17490,7 +17490,7 @@
         <v>559</v>
       </c>
       <c r="D354">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E354" s="9">
         <v>92521</v>
@@ -17568,7 +17568,7 @@
         <v>563</v>
       </c>
       <c r="D357">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E357" s="9">
         <v>92521</v>
@@ -17698,7 +17698,7 @@
         <v>573</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E362" s="9">
         <v>92521</v>
@@ -17932,7 +17932,7 @@
         <v>583</v>
       </c>
       <c r="D371">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E371" s="9">
         <v>92521</v>
@@ -18010,7 +18010,7 @@
         <v>587</v>
       </c>
       <c r="D374">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E374" s="9">
         <v>92521</v>
@@ -18036,7 +18036,7 @@
         <v>591</v>
       </c>
       <c r="D375">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E375" s="9">
         <v>92521</v>
@@ -18088,7 +18088,7 @@
         <v>594</v>
       </c>
       <c r="D377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E377" s="9">
         <v>92521</v>
@@ -18166,7 +18166,7 @@
         <v>599</v>
       </c>
       <c r="D380">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E380" s="9">
         <v>92521</v>
@@ -18192,7 +18192,7 @@
         <v>599</v>
       </c>
       <c r="D381">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E381" s="9">
         <v>92521</v>
@@ -18244,7 +18244,7 @@
         <v>599</v>
       </c>
       <c r="D383">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E383" s="9">
         <v>92521</v>
@@ -18270,7 +18270,7 @@
         <v>603</v>
       </c>
       <c r="D384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E384" s="9">
         <v>92521</v>
@@ -18348,7 +18348,7 @@
         <v>603</v>
       </c>
       <c r="D387">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E387" s="9">
         <v>92521</v>
@@ -18556,7 +18556,7 @@
         <v>618</v>
       </c>
       <c r="D395">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E395" s="9">
         <v>170500</v>
@@ -18582,7 +18582,7 @@
         <v>622</v>
       </c>
       <c r="D396">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E396" s="9">
         <v>170500</v>
@@ -18608,7 +18608,7 @@
         <v>622</v>
       </c>
       <c r="D397">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E397" s="9">
         <v>170500</v>
@@ -18738,7 +18738,7 @@
         <v>630</v>
       </c>
       <c r="D402">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E402" s="9">
         <v>170500</v>
@@ -19492,7 +19492,7 @@
         <v>675</v>
       </c>
       <c r="D431">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E431" s="9">
         <v>177500</v>
@@ -19518,7 +19518,7 @@
         <v>679</v>
       </c>
       <c r="D432">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E432" s="9">
         <v>177500</v>
@@ -20012,7 +20012,7 @@
         <v>708</v>
       </c>
       <c r="D451">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E451" s="9">
         <v>116500</v>
@@ -20038,7 +20038,7 @@
         <v>708</v>
       </c>
       <c r="D452">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="E452" s="9">
         <v>116500</v>
@@ -20064,7 +20064,7 @@
         <v>708</v>
       </c>
       <c r="D453">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E453" s="9">
         <v>116500</v>
@@ -20090,7 +20090,7 @@
         <v>712</v>
       </c>
       <c r="D454">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E454" s="9">
         <v>116500</v>
@@ -20116,7 +20116,7 @@
         <v>712</v>
       </c>
       <c r="D455">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E455" s="9">
         <v>116500</v>
@@ -20142,7 +20142,7 @@
         <v>712</v>
       </c>
       <c r="D456">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E456" s="9">
         <v>116500</v>
@@ -20168,7 +20168,7 @@
         <v>716</v>
       </c>
       <c r="D457">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E457" s="9">
         <v>116500</v>
@@ -20194,7 +20194,7 @@
         <v>716</v>
       </c>
       <c r="D458">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E458" s="9">
         <v>116500</v>
@@ -20220,7 +20220,7 @@
         <v>716</v>
       </c>
       <c r="D459">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E459" s="9">
         <v>116500</v>
@@ -20246,7 +20246,7 @@
         <v>720</v>
       </c>
       <c r="D460">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E460" s="9">
         <v>116500</v>
@@ -20272,7 +20272,7 @@
         <v>720</v>
       </c>
       <c r="D461">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E461" s="9">
         <v>116500</v>
@@ -20350,7 +20350,7 @@
         <v>726</v>
       </c>
       <c r="D464">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E464" s="9">
         <v>116500</v>
@@ -20376,7 +20376,7 @@
         <v>726</v>
       </c>
       <c r="D465">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E465" s="9">
         <v>116500</v>
@@ -20402,7 +20402,7 @@
         <v>726</v>
       </c>
       <c r="D466">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E466" s="9">
         <v>116500</v>
@@ -20428,7 +20428,7 @@
         <v>730</v>
       </c>
       <c r="D467">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E467" s="9">
         <v>116500</v>
@@ -20454,7 +20454,7 @@
         <v>730</v>
       </c>
       <c r="D468">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E468" s="9">
         <v>116500</v>
@@ -20480,7 +20480,7 @@
         <v>730</v>
       </c>
       <c r="D469">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E469" s="9">
         <v>116500</v>
@@ -20506,7 +20506,7 @@
         <v>734</v>
       </c>
       <c r="D470">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E470" s="9">
         <v>116500</v>
@@ -20532,7 +20532,7 @@
         <v>734</v>
       </c>
       <c r="D471">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E471" s="9">
         <v>116500</v>
@@ -20974,7 +20974,7 @@
         <v>760</v>
       </c>
       <c r="D488">
-        <v>128</v>
+        <v>294</v>
       </c>
       <c r="E488" s="9">
         <v>116500</v>
@@ -21000,7 +21000,7 @@
         <v>760</v>
       </c>
       <c r="D489">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E489" s="9">
         <v>116500</v>
@@ -21026,7 +21026,7 @@
         <v>760</v>
       </c>
       <c r="D490">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="E490" s="9">
         <v>116500</v>
@@ -21052,7 +21052,7 @@
         <v>764</v>
       </c>
       <c r="D491">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E491" s="9">
         <v>116500</v>
@@ -21078,7 +21078,7 @@
         <v>764</v>
       </c>
       <c r="D492">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="E492" s="9">
         <v>116500</v>
@@ -21104,7 +21104,7 @@
         <v>767</v>
       </c>
       <c r="D493">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E493" s="9">
         <v>116500</v>
@@ -21130,7 +21130,7 @@
         <v>767</v>
       </c>
       <c r="D494">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E494" s="9">
         <v>116500</v>
@@ -21156,7 +21156,7 @@
         <v>767</v>
       </c>
       <c r="D495">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E495" s="9">
         <v>116500</v>
@@ -21546,7 +21546,7 @@
         <v>790</v>
       </c>
       <c r="D510">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E510" s="9">
         <v>116500</v>
@@ -21780,7 +21780,7 @@
         <v>801</v>
       </c>
       <c r="D519">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E519" s="9">
         <v>116500</v>
@@ -21832,7 +21832,7 @@
         <v>805</v>
       </c>
       <c r="D521">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E521" s="9">
         <v>116500</v>
@@ -21910,7 +21910,7 @@
         <v>809</v>
       </c>
       <c r="D524">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E524" s="9">
         <v>116500</v>
@@ -22664,7 +22664,7 @@
         <v>852</v>
       </c>
       <c r="D553">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="E553" s="9">
         <v>116500</v>
@@ -22690,7 +22690,7 @@
         <v>852</v>
       </c>
       <c r="D554">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="E554" s="9">
         <v>116500</v>
@@ -22716,7 +22716,7 @@
         <v>855</v>
       </c>
       <c r="D555">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E555" s="9">
         <v>116500</v>
@@ -22742,7 +22742,7 @@
         <v>855</v>
       </c>
       <c r="D556">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E556" s="9">
         <v>116500</v>
@@ -23207,7 +23207,7 @@
         <v>886</v>
       </c>
       <c r="D574">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E574" s="9">
         <v>43000</v>
@@ -23415,7 +23415,7 @@
         <v>896</v>
       </c>
       <c r="D582">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E582" s="9">
         <v>43000</v>
@@ -23441,7 +23441,7 @@
         <v>896</v>
       </c>
       <c r="D583">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E583" s="9">
         <v>43000</v>
@@ -23467,7 +23467,7 @@
         <v>896</v>
       </c>
       <c r="D584">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E584" s="9">
         <v>43000</v>
@@ -23620,7 +23620,7 @@
         <v>908</v>
       </c>
       <c r="D590">
-        <v>4117</v>
+        <v>4096</v>
       </c>
       <c r="E590" s="9">
         <v>37000</v>
@@ -24009,7 +24009,7 @@
         <v>932</v>
       </c>
       <c r="D606">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E606" s="9">
         <v>171750</v>
@@ -24061,7 +24061,7 @@
         <v>937</v>
       </c>
       <c r="D608">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E608" s="9">
         <v>171750</v>
@@ -24087,7 +24087,7 @@
         <v>937</v>
       </c>
       <c r="D609">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E609" s="9">
         <v>171750</v>
@@ -24243,7 +24243,7 @@
         <v>946</v>
       </c>
       <c r="D615">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E615" s="9">
         <v>171750</v>
@@ -24321,7 +24321,7 @@
         <v>950</v>
       </c>
       <c r="D618">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E618" s="9">
         <v>171750</v>
@@ -24373,7 +24373,7 @@
         <v>954</v>
       </c>
       <c r="D620">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E620" s="9">
         <v>171750</v>
@@ -24451,7 +24451,7 @@
         <v>958</v>
       </c>
       <c r="D623">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E623" s="9">
         <v>171750</v>
@@ -24477,7 +24477,7 @@
         <v>958</v>
       </c>
       <c r="D624">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E624" s="9">
         <v>171750</v>
@@ -24503,7 +24503,7 @@
         <v>958</v>
       </c>
       <c r="D625">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E625" s="9">
         <v>171750</v>
@@ -24529,7 +24529,7 @@
         <v>958</v>
       </c>
       <c r="D626">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E626" s="9">
         <v>171750</v>
@@ -24607,7 +24607,7 @@
         <v>966</v>
       </c>
       <c r="D629">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E629" s="9">
         <v>171750</v>
@@ -24633,7 +24633,7 @@
         <v>966</v>
       </c>
       <c r="D630">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E630" s="9">
         <v>171750</v>
@@ -24737,7 +24737,7 @@
         <v>973</v>
       </c>
       <c r="D634">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E634" s="9">
         <v>171750</v>
@@ -24789,7 +24789,7 @@
         <v>976</v>
       </c>
       <c r="D636">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E636" s="9">
         <v>116300</v>
@@ -24815,7 +24815,7 @@
         <v>976</v>
       </c>
       <c r="D637">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E637" s="9">
         <v>116300</v>
@@ -24867,7 +24867,7 @@
         <v>976</v>
       </c>
       <c r="D639">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E639" s="9">
         <v>116300</v>
@@ -24997,7 +24997,7 @@
         <v>986</v>
       </c>
       <c r="D644">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E644" s="9">
         <v>30000</v>
@@ -25049,7 +25049,7 @@
         <v>989</v>
       </c>
       <c r="D646">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E646" s="9">
         <v>30000</v>
@@ -25621,7 +25621,7 @@
         <v>1018</v>
       </c>
       <c r="D668">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E668" s="9">
         <v>161750</v>
@@ -25699,7 +25699,7 @@
         <v>1024</v>
       </c>
       <c r="D671">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E671" s="9">
         <v>161750</v>
@@ -25777,7 +25777,7 @@
         <v>1024</v>
       </c>
       <c r="D674">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E674" s="9">
         <v>161750</v>
@@ -25829,7 +25829,7 @@
         <v>1029</v>
       </c>
       <c r="D676">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E676" s="9">
         <v>161750</v>
@@ -25855,7 +25855,7 @@
         <v>1029</v>
       </c>
       <c r="D677">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E677" s="9">
         <v>161750</v>
@@ -25881,7 +25881,7 @@
         <v>1029</v>
       </c>
       <c r="D678">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E678" s="9">
         <v>161750</v>
@@ -25907,7 +25907,7 @@
         <v>1034</v>
       </c>
       <c r="D679">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E679" s="9">
         <v>161750</v>
@@ -26141,7 +26141,7 @@
         <v>1046</v>
       </c>
       <c r="D688">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E688" s="9">
         <v>161750</v>
@@ -26167,7 +26167,7 @@
         <v>1046</v>
       </c>
       <c r="D689">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E689" s="9">
         <v>161750</v>
@@ -26219,7 +26219,7 @@
         <v>1046</v>
       </c>
       <c r="D691">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E691" s="9">
         <v>161750</v>
@@ -26427,7 +26427,7 @@
         <v>1059</v>
       </c>
       <c r="D699">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E699" s="9">
         <v>180000</v>
@@ -26609,7 +26609,7 @@
         <v>1072</v>
       </c>
       <c r="D706">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E706" s="9">
         <v>180000</v>
@@ -27415,7 +27415,7 @@
         <v>1120</v>
       </c>
       <c r="D737">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E737" s="9">
         <v>296500</v>
@@ -27571,7 +27571,7 @@
         <v>1132</v>
       </c>
       <c r="D743">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E743" s="9">
         <v>296500</v>
@@ -28013,7 +28013,7 @@
         <v>1157</v>
       </c>
       <c r="D760">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E760" s="9">
         <v>296500</v>
@@ -28091,7 +28091,7 @@
         <v>1157</v>
       </c>
       <c r="D763">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E763" s="9">
         <v>296500</v>
@@ -28299,7 +28299,7 @@
         <v>1168</v>
       </c>
       <c r="D771">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E771" s="9">
         <v>296500</v>
@@ -28767,7 +28767,7 @@
         <v>1200</v>
       </c>
       <c r="D789">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E789" s="9">
         <v>296500</v>
@@ -28819,7 +28819,7 @@
         <v>1200</v>
       </c>
       <c r="D791">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E791" s="9">
         <v>296500</v>
@@ -29694,7 +29694,7 @@
         <v>1252</v>
       </c>
       <c r="D825">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E825" s="9">
         <v>81713</v>
@@ -29720,7 +29720,7 @@
         <v>1252</v>
       </c>
       <c r="D826">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E826" s="9">
         <v>81713</v>
@@ -30812,7 +30812,7 @@
         <v>1306</v>
       </c>
       <c r="D868">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E868" s="9">
         <v>54198</v>
@@ -32294,7 +32294,7 @@
         <v>1395</v>
       </c>
       <c r="D925">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E925" s="9">
         <v>186000</v>
@@ -32398,7 +32398,7 @@
         <v>1403</v>
       </c>
       <c r="D929">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E929" s="9">
         <v>300000</v>
@@ -32891,7 +32891,7 @@
         <v>1433</v>
       </c>
       <c r="D949">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E949" s="9">
         <v>240000</v>
@@ -33229,7 +33229,7 @@
         <v>1453</v>
       </c>
       <c r="D962">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E962" s="9">
         <v>240000</v>
@@ -33463,7 +33463,7 @@
         <v>1468</v>
       </c>
       <c r="D971">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E971" s="9">
         <v>240000</v>
@@ -33489,7 +33489,7 @@
         <v>1468</v>
       </c>
       <c r="D972">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E972" s="9">
         <v>240000</v>
@@ -33541,7 +33541,7 @@
         <v>1468</v>
       </c>
       <c r="D974">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E974" s="9">
         <v>240000</v>
@@ -33723,7 +33723,7 @@
         <v>1482</v>
       </c>
       <c r="D981">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E981" s="9">
         <v>240000</v>
@@ -33801,7 +33801,7 @@
         <v>1482</v>
       </c>
       <c r="D984">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E984" s="9">
         <v>240000</v>
@@ -33853,7 +33853,7 @@
         <v>1487</v>
       </c>
       <c r="D986">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E986" s="9">
         <v>240000</v>
@@ -33983,7 +33983,7 @@
         <v>1492</v>
       </c>
       <c r="D991">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E991" s="9">
         <v>240000</v>
@@ -34113,7 +34113,7 @@
         <v>1504</v>
       </c>
       <c r="D996">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E996" s="9">
         <v>240000</v>
@@ -34243,7 +34243,7 @@
         <v>1509</v>
       </c>
       <c r="D1001">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E1001" s="9">
         <v>240000</v>
@@ -34503,7 +34503,7 @@
         <v>1520</v>
       </c>
       <c r="D1011">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1011" s="9">
         <v>240000</v>
@@ -34529,7 +34529,7 @@
         <v>1520</v>
       </c>
       <c r="D1012">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1012" s="9">
         <v>240000</v>
@@ -34555,7 +34555,7 @@
         <v>1525</v>
       </c>
       <c r="D1013">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1013" s="9">
         <v>240000</v>
@@ -34607,7 +34607,7 @@
         <v>1525</v>
       </c>
       <c r="D1015">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E1015" s="9">
         <v>240000</v>
@@ -34633,7 +34633,7 @@
         <v>1529</v>
       </c>
       <c r="D1016">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E1016" s="9">
         <v>240000</v>
@@ -34737,7 +34737,7 @@
         <v>1532</v>
       </c>
       <c r="D1020">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E1020" s="9">
         <v>240000</v>
@@ -34815,7 +34815,7 @@
         <v>1536</v>
       </c>
       <c r="D1023">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1023" s="9">
         <v>240000</v>
@@ -34945,7 +34945,7 @@
         <v>1544</v>
       </c>
       <c r="D1028">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E1028" s="9">
         <v>240000</v>
@@ -36083,7 +36083,7 @@
         <v>1615</v>
       </c>
       <c r="D1072">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1072" s="9">
         <v>261500</v>
@@ -36109,7 +36109,7 @@
         <v>1615</v>
       </c>
       <c r="D1073">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1073" s="9">
         <v>261500</v>
@@ -37097,7 +37097,7 @@
         <v>1670</v>
       </c>
       <c r="D1111">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1111" s="9">
         <v>261500</v>
@@ -37461,7 +37461,7 @@
         <v>1691</v>
       </c>
       <c r="D1125">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1125" s="9">
         <v>261500</v>
@@ -37487,7 +37487,7 @@
         <v>1691</v>
       </c>
       <c r="D1126">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1126" s="9">
         <v>261500</v>
@@ -37695,7 +37695,7 @@
         <v>1702</v>
       </c>
       <c r="D1134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1134" s="9">
         <v>261500</v>
@@ -37955,7 +37955,7 @@
         <v>1716</v>
       </c>
       <c r="D1144">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1144" s="9">
         <v>261500</v>
@@ -38397,7 +38397,7 @@
         <v>1747</v>
       </c>
       <c r="D1161">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1161" s="9">
         <v>261500</v>
@@ -38449,7 +38449,7 @@
         <v>1670</v>
       </c>
       <c r="D1163">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1163" s="9">
         <v>261500</v>
@@ -38787,7 +38787,7 @@
         <v>1770</v>
       </c>
       <c r="D1176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1176" s="9">
         <v>265500</v>
@@ -38943,7 +38943,7 @@
         <v>1775</v>
       </c>
       <c r="D1182">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E1182" s="9">
         <v>265500</v>
@@ -39021,7 +39021,7 @@
         <v>1781</v>
       </c>
       <c r="D1185">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1185" s="9">
         <v>265500</v>
@@ -39047,7 +39047,7 @@
         <v>1781</v>
       </c>
       <c r="D1186">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1186" s="9">
         <v>265500</v>
@@ -39125,7 +39125,7 @@
         <v>1788</v>
       </c>
       <c r="D1189">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1189" s="9">
         <v>265500</v>
@@ -39593,7 +39593,7 @@
         <v>1814</v>
       </c>
       <c r="D1207">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E1207" s="9">
         <v>265500</v>
@@ -39671,7 +39671,7 @@
         <v>1814</v>
       </c>
       <c r="D1210">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E1210" s="9">
         <v>265500</v>
@@ -39798,7 +39798,7 @@
         <v>1827</v>
       </c>
       <c r="D1215">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E1215" s="9">
         <v>10772</v>
@@ -40705,7 +40705,7 @@
         <v>1881</v>
       </c>
       <c r="D1250">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E1250" s="9">
         <v>66500</v>
@@ -40731,7 +40731,7 @@
         <v>1883</v>
       </c>
       <c r="D1251">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1251" s="9">
         <v>85500</v>
@@ -40757,7 +40757,7 @@
         <v>1885</v>
       </c>
       <c r="D1252">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1252" s="9">
         <v>120500</v>
@@ -41395,7 +41395,7 @@
         <v>1924</v>
       </c>
       <c r="D1277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1277" s="9">
         <v>255500</v>
@@ -41499,7 +41499,7 @@
         <v>1931</v>
       </c>
       <c r="D1281">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E1281" s="9">
         <v>255500</v>
@@ -41525,7 +41525,7 @@
         <v>1931</v>
       </c>
       <c r="D1282">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1282" s="9">
         <v>255500</v>
@@ -41551,7 +41551,7 @@
         <v>1931</v>
       </c>
       <c r="D1283">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1283" s="9">
         <v>255500</v>
@@ -41629,7 +41629,7 @@
         <v>1938</v>
       </c>
       <c r="D1286">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1286" s="9">
         <v>255500</v>
@@ -41655,7 +41655,7 @@
         <v>1938</v>
       </c>
       <c r="D1287">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1287" s="9">
         <v>255500</v>
@@ -41681,7 +41681,7 @@
         <v>1938</v>
       </c>
       <c r="D1288">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1288" s="9">
         <v>255500</v>
@@ -41785,7 +41785,7 @@
         <v>1942</v>
       </c>
       <c r="D1292">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1292" s="9">
         <v>255500</v>
@@ -42227,7 +42227,7 @@
         <v>1972</v>
       </c>
       <c r="D1309">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1309" s="9">
         <v>255500</v>
@@ -42591,7 +42591,7 @@
         <v>1993</v>
       </c>
       <c r="D1323">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E1323" s="9">
         <v>255500</v>
@@ -42617,7 +42617,7 @@
         <v>1993</v>
       </c>
       <c r="D1324">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1324" s="9">
         <v>255500</v>
@@ -42643,7 +42643,7 @@
         <v>1993</v>
       </c>
       <c r="D1325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1325" s="9">
         <v>255500</v>
@@ -43111,7 +43111,7 @@
         <v>2023</v>
       </c>
       <c r="D1343">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1343" s="9">
         <v>255500</v>
@@ -43163,7 +43163,7 @@
         <v>2028</v>
       </c>
       <c r="D1345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1345" s="9">
         <v>255500</v>
@@ -43319,7 +43319,7 @@
         <v>2037</v>
       </c>
       <c r="D1351">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1351" s="9">
         <v>255500</v>
@@ -43345,7 +43345,7 @@
         <v>2037</v>
       </c>
       <c r="D1352">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1352" s="9">
         <v>255500</v>
@@ -43371,7 +43371,7 @@
         <v>2037</v>
       </c>
       <c r="D1353">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1353" s="9">
         <v>255500</v>
@@ -43475,7 +43475,7 @@
         <v>2045</v>
       </c>
       <c r="D1357">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1357" s="9">
         <v>255500</v>
@@ -43527,7 +43527,7 @@
         <v>2045</v>
       </c>
       <c r="D1359">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1359" s="9">
         <v>255500</v>
@@ -43553,7 +43553,7 @@
         <v>2045</v>
       </c>
       <c r="D1360">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E1360" s="9">
         <v>255500</v>
@@ -43631,7 +43631,7 @@
         <v>2053</v>
       </c>
       <c r="D1363">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E1363" s="9">
         <v>255500</v>
@@ -43683,7 +43683,7 @@
         <v>2053</v>
       </c>
       <c r="D1365">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1365" s="9">
         <v>255500</v>
@@ -43813,7 +43813,7 @@
         <v>2060</v>
       </c>
       <c r="D1370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1370" s="9">
         <v>255500</v>
@@ -44047,7 +44047,7 @@
         <v>2074</v>
       </c>
       <c r="D1379">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E1379" s="9">
         <v>255500</v>
@@ -44177,7 +44177,7 @@
         <v>2078</v>
       </c>
       <c r="D1384">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1384" s="9">
         <v>255500</v>
@@ -44203,7 +44203,7 @@
         <v>2082</v>
       </c>
       <c r="D1385">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1385" s="9">
         <v>255500</v>
@@ -44359,7 +44359,7 @@
         <v>2087</v>
       </c>
       <c r="D1391">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E1391" s="9">
         <v>255500</v>
@@ -45006,7 +45006,7 @@
         <v>2129</v>
       </c>
       <c r="D1416">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1416" s="9">
         <v>265500</v>
@@ -45240,7 +45240,7 @@
         <v>2143</v>
       </c>
       <c r="D1425">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E1425" s="9">
         <v>265500</v>
@@ -45370,7 +45370,7 @@
         <v>2150</v>
       </c>
       <c r="D1430">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E1430" s="9">
         <v>265500</v>
@@ -45396,7 +45396,7 @@
         <v>2150</v>
       </c>
       <c r="D1431">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E1431" s="9">
         <v>265500</v>
@@ -45422,7 +45422,7 @@
         <v>2150</v>
       </c>
       <c r="D1432">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E1432" s="9">
         <v>265500</v>
@@ -45604,7 +45604,7 @@
         <v>2154</v>
       </c>
       <c r="D1439">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1439" s="9">
         <v>265500</v>
@@ -45630,7 +45630,7 @@
         <v>2164</v>
       </c>
       <c r="D1440">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E1440" s="9">
         <v>265500</v>
@@ -45656,7 +45656,7 @@
         <v>2164</v>
       </c>
       <c r="D1441">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E1441" s="9">
         <v>265500</v>
@@ -45682,7 +45682,7 @@
         <v>2167</v>
       </c>
       <c r="D1442">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1442" s="9">
         <v>265500</v>
@@ -45734,7 +45734,7 @@
         <v>2167</v>
       </c>
       <c r="D1444">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E1444" s="9">
         <v>265500</v>
@@ -45838,7 +45838,7 @@
         <v>2175</v>
       </c>
       <c r="D1448">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1448" s="9">
         <v>265500</v>
@@ -45864,7 +45864,7 @@
         <v>2175</v>
       </c>
       <c r="D1449">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1449" s="9">
         <v>265500</v>
@@ -45942,7 +45942,7 @@
         <v>2179</v>
       </c>
       <c r="D1452">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1452" s="9">
         <v>265500</v>
@@ -45968,7 +45968,7 @@
         <v>2179</v>
       </c>
       <c r="D1453">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1453" s="9">
         <v>265500</v>
@@ -45994,7 +45994,7 @@
         <v>2183</v>
       </c>
       <c r="D1454">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1454" s="9">
         <v>265500</v>
@@ -46020,7 +46020,7 @@
         <v>2183</v>
       </c>
       <c r="D1455">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1455" s="9">
         <v>265500</v>
@@ -46046,7 +46046,7 @@
         <v>2186</v>
       </c>
       <c r="D1456">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E1456" s="9">
         <v>265500</v>
@@ -46072,7 +46072,7 @@
         <v>2186</v>
       </c>
       <c r="D1457">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1457" s="9">
         <v>265500</v>
@@ -46202,7 +46202,7 @@
         <v>2195</v>
       </c>
       <c r="D1462">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E1462" s="9">
         <v>265500</v>
@@ -46280,7 +46280,7 @@
         <v>2195</v>
       </c>
       <c r="D1465">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1465" s="9">
         <v>265500</v>
@@ -46566,7 +46566,7 @@
         <v>2214</v>
       </c>
       <c r="D1476">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E1476" s="9">
         <v>265500</v>
@@ -46592,7 +46592,7 @@
         <v>2214</v>
       </c>
       <c r="D1477">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E1477" s="9">
         <v>265500</v>
@@ -47060,7 +47060,7 @@
         <v>2238</v>
       </c>
       <c r="D1495">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1495" s="9">
         <v>228000</v>
@@ -47164,7 +47164,7 @@
         <v>2247</v>
       </c>
       <c r="D1499">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1499" s="9">
         <v>228000</v>
@@ -47216,7 +47216,7 @@
         <v>2247</v>
       </c>
       <c r="D1501">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1501" s="9">
         <v>228000</v>
@@ -47242,7 +47242,7 @@
         <v>2251</v>
       </c>
       <c r="D1502">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1502" s="9">
         <v>228000</v>
@@ -47320,7 +47320,7 @@
         <v>2255</v>
       </c>
       <c r="D1505">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1505" s="9">
         <v>228000</v>
@@ -48672,7 +48672,7 @@
         <v>2324</v>
       </c>
       <c r="D1557">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E1557" s="9">
         <v>228000</v>
@@ -48802,7 +48802,7 @@
         <v>2331</v>
       </c>
       <c r="D1562">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1562" s="9">
         <v>228000</v>
@@ -49270,7 +49270,7 @@
         <v>2361</v>
       </c>
       <c r="D1580">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1580" s="9">
         <v>314500</v>
@@ -49400,7 +49400,7 @@
         <v>2370</v>
       </c>
       <c r="D1585">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E1585" s="9">
         <v>75555</v>
@@ -49426,7 +49426,7 @@
         <v>2372</v>
       </c>
       <c r="D1586">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E1586" s="9">
         <v>62000</v>
@@ -49452,7 +49452,7 @@
         <v>2374</v>
       </c>
       <c r="D1587">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="E1587" s="9">
         <v>65000</v>
@@ -49478,7 +49478,7 @@
         <v>2376</v>
       </c>
       <c r="D1588">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1588" s="9">
         <v>296500</v>
@@ -49504,7 +49504,7 @@
         <v>2376</v>
       </c>
       <c r="D1589">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1589" s="9">
         <v>296500</v>
@@ -49530,7 +49530,7 @@
         <v>2376</v>
       </c>
       <c r="D1590">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1590" s="9">
         <v>296500</v>
@@ -49686,7 +49686,7 @@
         <v>2384</v>
       </c>
       <c r="D1596">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1596" s="9">
         <v>296500</v>
@@ -50388,7 +50388,7 @@
         <v>2425</v>
       </c>
       <c r="D1623">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E1623" s="9">
         <v>81000</v>
@@ -50414,7 +50414,7 @@
         <v>2425</v>
       </c>
       <c r="D1624">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="E1624" s="9">
         <v>81000</v>
@@ -50440,7 +50440,7 @@
         <v>2428</v>
       </c>
       <c r="D1625">
-        <v>5</v>
+        <v>146</v>
       </c>
       <c r="E1625" s="9">
         <v>81000</v>
@@ -50466,7 +50466,7 @@
         <v>2428</v>
       </c>
       <c r="D1626">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="E1626" s="9">
         <v>81000</v>
